--- a/游戏demo/内容编辑器实际Demo表格.xlsx
+++ b/游戏demo/内容编辑器实际Demo表格.xlsx
@@ -4,7 +4,7 @@
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
     <sheet name="路线配置" sheetId="2" r:id="rId2"/>
-    <sheet name="用户画像" sheetId="3" r:id="rId3"/>
+    <sheet name="猫群画像" sheetId="3" r:id="rId3"/>
     <sheet name="关卡参数" sheetId="4" r:id="rId4"/>
     <sheet name="卡牌参数" sheetId="5" r:id="rId5"/>
     <sheet name="事件参数" sheetId="6" r:id="rId6"/>
@@ -96,7 +96,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>同步游戏平衡调整后的 iPhone 参数。</t>
+          <t>同步喵喵世界观迁移后的默认参数。</t>
         </is>
       </c>
     </row>
@@ -161,17 +161,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>照护、康复、慢病管理与家庭协同。</t>
+          <t>长者猫照护、康复、慢病提醒与家庭协同。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -198,17 +198,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>面向企业、创作者与专业岗位的流程提效。</t>
+          <t>面向工坊、创作者与专业岗位的自动化提效。</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -235,12 +235,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -272,17 +272,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>真实公司故事线</t>
+          <t>喵史映射路线</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>真实产品故事线：Project Purple 从秘密立项到 2007-06-29 发售。</t>
+          <t>喵史映射路线：紫铃计划从秘密立项到喵历 2007-06-29 发售。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -368,7 +368,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>慢病老人</t>
+          <t>慢病老猫</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -410,7 +410,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>子女照护者</t>
+          <t>小猫照护者</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -452,7 +452,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>社区医生</t>
+          <t>街区猫医</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>康复机构</t>
+          <t>康复猫舍</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>活跃退休者</t>
+          <t>活跃银须猫</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>增长人群</t>
+          <t>增长猫群</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>保险顾问</t>
+          <t>鱼干保单顾问</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>护理站长</t>
+          <t>护理窝长</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>空巢老人</t>
+          <t>独居老猫</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>药房店员</t>
+          <t>草药铺店猫</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>养老院采购</t>
+          <t>养老猫舍采购</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>康复教练</t>
+          <t>康复教练猫</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>银发健康</t>
+          <t>银须照护</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>家庭护士</t>
+          <t>上门护士猫</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>独立开发者</t>
+          <t>独立爪匠</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>中小老板</t>
+          <t>小工坊掌柜</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>一线运营</t>
+          <t>一线运营猫</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>内容团队</t>
+          <t>内容猫班</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>增长人群</t>
+          <t>增长猫群</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>数据分析师</t>
+          <t>数账分析猫</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>外包团队</t>
+          <t>外包猫队</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>销售主管</t>
+          <t>鱼市销售长</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>法务经理</t>
+          <t>猫律经理</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>设计师</t>
+          <t>织界面猫</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>客服团队</t>
+          <t>客服猫群</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>咨询顾问</t>
+          <t>军师顾问猫</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AI效率工具</t>
+          <t>灵爪效率工坊</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>学生社群</t>
+          <t>学徒猫社群</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>新锐白领</t>
+          <t>新锐白爪猫</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>精致妈妈</t>
+          <t>精致猫妈妈</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>户外爱好者</t>
+          <t>屋顶探险猫</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>社区团长</t>
+          <t>街区团长猫</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>礼品采购</t>
+          <t>礼盒采购猫</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>环保达人</t>
+          <t>绿爪达人</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>便利店店主</t>
+          <t>巷口小店主</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>校园社群</t>
+          <t>学堂猫社群</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>企业行政</t>
+          <t>工坊行政猫</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>材料供应商</t>
+          <t>竹纤供应猫</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>直播买手</t>
+          <t>直播带货猫</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>绿色消费</t>
+          <t>绿爪市集</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>设计集合店</t>
+          <t>设计猫集店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2008,22 +2008,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>立项做DEMO</t>
+          <t>搭建爪印样机</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>样机</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>核心工作：可演示 Demo</t>
+          <t>核心工作：可演示爪印样机</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Demo剩余工作</t>
+          <t>样机剩余工作</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2043,17 +2043,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>评审阻力</t>
+          <t>评审毛结</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Deadline压力</t>
+          <t>截止铃压力</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>先做出能说明核心价值的 Demo。</t>
+          <t>先做出能让猫群看懂核心价值的爪印样机。</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2095,22 +2095,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>说服投资人</t>
+          <t>说服鱼干金主</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>融资</t>
+          <t>筹鱼</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>核心工作：投资人疑虑</t>
+          <t>核心工作：鱼干金主疑虑</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>投资人疑虑</t>
+          <t>金主疑虑</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>质疑点</t>
+          <t>挑刺纸条</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>把市场、团队、模型和路线讲清楚。</t>
+          <t>把鱼市、猫窝团队、收益模型和路线讲清楚。</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>产品研发</t>
+          <t>爪品研发</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>核心工作：研发待办</t>
+          <t>核心工作：爪品研发待办</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>技术债</t>
+          <t>毛线技术债</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>把 Demo 打磨成可用产品。</t>
+          <t>把爪印样机打磨成猫群愿意日常使用的爪品。</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>供应商谈判</t>
+          <t>鱼市供应谈判</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>核心工作：供应商分歧</t>
+          <t>核心工作：供货猫分歧</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>合同障碍</t>
+          <t>契约毛结</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>确定成本、交期、质量和账期。</t>
+          <t>确定鱼干成本、交期、品质和账期。</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2356,22 +2356,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>量产生产期</t>
+          <t>批量造爪期</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>量产</t>
+          <t>量造</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>核心工作：生产风险</t>
+          <t>核心工作：批量造爪风险</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>生产风险</t>
+          <t>造爪风险</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>良率问题</t>
+          <t>良率毛病</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>把样品变成稳定批量交付。</t>
+          <t>把样品变成能稳定批量交付的猫窝产物。</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2443,17 +2443,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>宣发</t>
+          <t>传令鸟造势</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>宣发</t>
+          <t>造势</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>核心工作：市场声量缺口</t>
+          <t>核心工作：鱼市声量缺口</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>传播噪音</t>
+          <t>传闻杂音</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>用有限预算打出发售前关注。</t>
+          <t>用有限鱼干预算打出发售前关注。</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>最后发售结束</t>
+          <t>最终开摊发售</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>核心工作：发售关键事项</t>
+          <t>核心工作：开摊关键事项</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>现场问题</t>
+          <t>摊位问题</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>完成最终发售和收尾复盘。</t>
+          <t>完成最终开摊发售和收尾复盘。</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Project Purple立项</t>
+          <t>紫铃计划立项</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>核心工作：多点触控方向决策</t>
+          <t>核心工作：多爪触控方向决策</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>键盘惯性</t>
+          <t>实体键惯性</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>从 iPod、手机和互联网终端的交叉点里，押注全触控设备。</t>
+          <t>从随身唱盒、传声器和织网终端的交叉点里，押注全爪触控设备。</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>运营商谈判</t>
+          <t>信号塔盟谈判</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>塔盟</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>核心工作：运营商控制权</t>
+          <t>核心工作：信号塔盟控制权</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>渠道条款</t>
+          <t>塔盟条款</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>争取罕见的硬件、软件和营销自主权，同时承受独家合作压力。</t>
+          <t>争取罕见的硬件、软件和营销自主权，同时承受独家塔盟合作压力。</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OS X触控移植</t>
+          <t>X毛线系统移植</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>核心工作：手机级 OS X</t>
+          <t>核心工作：掌上级 X毛线系统</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>内存约束</t>
+          <t>记忆毛球约束</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>把桌面级系统重写成能在手机芯片、触控和电池限制里运行的版本。</t>
+          <t>把桌面级系统重写成能在掌上芯片、爪触和电池限制里运行的版本。</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2878,17 +2878,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Macworld发布演示</t>
+          <t>大喵展演会演示</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>发布</t>
+          <t>展演</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>核心工作：现场演示风险</t>
+          <t>核心工作：现场展演风险</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Demo故障</t>
+          <t>样机故障</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>在 2007-01-09 的发布会上证明：它是一台 iPod、一部电话和一个互联网通讯器。</t>
+          <t>在喵历 2007-01-09 的展演会上证明：它是一台随身唱盒、一部传声器和一个织网通讯器。</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>玻璃与续航冲刺</t>
+          <t>玻璃爪面与续航冲刺</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>核心工作：耐用玻璃与电池</t>
+          <t>核心工作：耐用玻璃爪面与电池</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>刮痕问题</t>
+          <t>爪痕问题</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>在发售前把塑料表面换成抗刮玻璃，并提升通话和媒体续航。</t>
+          <t>在发售前把塑料表面换成抗爪玻璃，并提升通话和影音续航。</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Web App生态准备</t>
+          <t>织网应用生态准备</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>核心工作：第三方应用路径</t>
+          <t>核心工作：第三方爪匠应用路径</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>开发者疑虑</t>
+          <t>爪匠疑虑</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>用 Safari Web 2.0 应用先打开第三方生态入口，为发售前补足软件故事。</t>
+          <t>用远巡浏览器织网应用先打开第三方生态入口，为发售前补足软件故事。</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2007-06-29发售</t>
+          <t>喵历 2007-06-29发售</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>核心工作：首发上市执行</t>
+          <t>核心工作：首发开摊执行</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>完成门店排队、合约激活、媒体评测和首批用户交付。</t>
+          <t>完成咬果门店排队、合约激活、传令鸟评测和首批猫群交付。</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>招募工程师</t>
+          <t>招募爪印工程师</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>产品经理</t>
+          <t>猫产品掌柜</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UI设计师</t>
+          <t>界面织毛师</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>销售合伙人</t>
+          <t>鱼市合伙猫</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>核心工作 -4，资金 +2。</t>
+          <t>核心工作 -4，鱼干 +2。</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>供应链专家</t>
+          <t>鱼市供应专家</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>法务顾问</t>
+          <t>猫律顾问</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>技术预研</t>
+          <t>爪研试验</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>架构重构</t>
+          <t>毛线架构重整</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>数据分析</t>
+          <t>鱼骨数据分析</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>自动化工具</t>
+          <t>自动爪具</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天使资金</t>
+          <t>鱼干天使</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>资金 +6，剩余时间 +2。</t>
+          <t>鱼干 +6，剩余时间 +2。</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>精打细算</t>
+          <t>精算鱼干</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>资金 +3，时间缓冲 +2。</t>
+          <t>鱼干 +3，时间缓冲 +2。</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>外包开发</t>
+          <t>外包猫队</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>资金 -3，核心工作 -8。</t>
+          <t>鱼干 -3，核心工作 -8。</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>争取时间</t>
+          <t>多争几天</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>排期缓冲</t>
+          <t>猫窝排期垫</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>砍掉非核心</t>
+          <t>剪掉花哨毛线</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>导师背书</t>
+          <t>老猫导师背书</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>通宵冲刺</t>
+          <t>夜巡冲刺</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>团队对齐</t>
+          <t>猫窝对齐</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>众筹预热</t>
+          <t>众筹鱼摊</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>资金 +4，核心工作 -4。</t>
+          <t>鱼干 +4，核心工作 -4。</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>多点触控原型</t>
+          <t>多爪触控原型</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Purple保密室</t>
+          <t>紫铃保密窝</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OS X瘦身</t>
+          <t>X毛线瘦身</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cingular谈判</t>
+          <t>信号塔盟谈判</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>资金 +5，核心工作 -4。</t>
+          <t>鱼干 +5，核心工作 -4。</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>可视语音信箱</t>
+          <t>可视留声鱼箱</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>光学玻璃表面</t>
+          <t>光学玻璃爪面</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>八小时通话</t>
+          <t>八小时传声</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>移动Safari</t>
+          <t>远巡浏览器</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>发布会走台</t>
+          <t>展演会走台</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>黄金演示路径</t>
+          <t>黄金演示爪径</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>演示数据布置</t>
+          <t>演示鱼骨布置</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>射频测试室</t>
+          <t>信号测试窝</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ARM芯片预算</t>
+          <t>掌芯预算</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>资金 -2，核心工作 -9。</t>
+          <t>鱼干 -2，核心工作 -9。</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>硬软隔离协作</t>
+          <t>硬软隔窝协作</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Web App方案</t>
+          <t>织网应用方案</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>iTunes同步闭环</t>
+          <t>唱盒同步闭环</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>核心工作 -6，资金 +2。</t>
+          <t>核心工作 -6，鱼干 +2。</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>门店首发排队</t>
+          <t>咬果门店排队</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>资金 +3，核心工作 -4。</t>
+          <t>鱼干 +3，核心工作 -4。</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>媒体评测机</t>
+          <t>传令鸟评测机</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>激活流程预案</t>
+          <t>激活流程彩排</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>无说明书体验</t>
+          <t>无纸卷体验</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MVP切片</t>
+          <t>最小爪品切片</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>可点击原型</t>
+          <t>可点爪原型</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10次访谈</t>
+          <t>10次猫群访谈</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>融资BP</t>
+          <t>筹鱼干画册</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>核心工作 -7，资金 +2。</t>
+          <t>核心工作 -7，鱼干 +2。</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>条款清单</t>
+          <t>契约条款清单</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>领投背书</t>
+          <t>领投金主背书</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>资金 +8，核心工作 -4。</t>
+          <t>鱼干 +8，核心工作 -4。</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>测试矩阵</t>
+          <t>爪测矩阵</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>内测版本</t>
+          <t>猫窝内测版</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>模块重构</t>
+          <t>毛线模块重整</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>验厂清单</t>
+          <t>验窝清单</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>备选供应商</t>
+          <t>备选供货猫</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>账期谈判</t>
+          <t>鱼干账期谈判</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>资金 +5，压力 -1。</t>
+          <t>鱼干 +5，压力 -1。</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>质检抽样</t>
+          <t>爪品质检抽样</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>产线爬坡</t>
+          <t>造爪线爬坡</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>需求预测</t>
+          <t>鱼市需求预测</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>抽 2 张牌，资金 +2。</t>
+          <t>抽 2 张牌，鱼干 +2。</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KOL种草</t>
+          <t>头部猫种草</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>媒体发布</t>
+          <t>传令鸟发布</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>核心工作 -10，资金 +2。</t>
+          <t>核心工作 -10，鱼干 +2。</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>社群裂变</t>
+          <t>猫群裂变</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>手指优先</t>
+          <t>爪尖优先</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>取消实体键盘</t>
+          <t>取消实体按键板</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Purple冲刺</t>
+          <t>紫铃冲刺</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>保留产品控制权</t>
+          <t>保留爪品控制权</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>语音信箱让步</t>
+          <t>留声鱼箱让步</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>服务收入分成</t>
+          <t>服务鱼干分成</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>资金 +9。</t>
+          <t>鱼干 +9。</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SpringBoard雏形</t>
+          <t>猫跳板界面雏形</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>软键盘校准</t>
+          <t>软按键板校准</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>内存瘦身表</t>
+          <t>记忆毛球瘦身表</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>致电康宁</t>
+          <t>呼叫晶爪玻璃坊</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>续航对比图</t>
+          <t>续航对比爪图</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>射频模拟器</t>
+          <t>信号模拟窝</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>三合一叙事</t>
+          <t>三合一喵叙事</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>核心工作 -7，资金 +2。</t>
+          <t>核心工作 -7，鱼干 +2。</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>演示重置脚本</t>
+          <t>演示重置爪本</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>媒体震动</t>
+          <t>传令鸟震动</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>资金 +4，核心工作 -5。</t>
+          <t>鱼干 +4，核心工作 -5。</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Safari应用入口</t>
+          <t>远巡应用入口</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Web 2.0说法</t>
+          <t>织网2.0说法</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>政策补贴窗口</t>
+          <t>鱼干补助窗口</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>监管口径变化</t>
+          <t>巡逻口径变化</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>疫情反复</t>
+          <t>猫窝隔离波</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>关键物料短缺</t>
+          <t>关键鱼箱短缺</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>媒体突然关注</t>
+          <t>传令鸟突然关注</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>平台规则调整</t>
+          <t>猫台规则调整</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>人才市场松动</t>
+          <t>猫才市场松动</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>竞品抢先发布</t>
+          <t>竞品抢先开摊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>模拟创业路线</t>
+          <t>自由喵创路线</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5993,22 +5993,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2007-01-09：Apple Inc.登场</t>
+          <t>喵历 2007-01-09：咬果工坊登场</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>历史时间线事件</t>
+          <t>喵史时间线事件</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2007-01-09</t>
+          <t/>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -6025,22 +6025,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2007-01-10：Cisco商标诉讼</t>
+          <t>喵历 2007-01-10：蓝桥商号名号争议</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>历史时间线事件</t>
+          <t>喵史时间线事件</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2007-01-10</t>
+          <t/>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -6057,22 +6057,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2007-05-17：FCC批准</t>
+          <t>喵历 2007-05-17：高塔议会通行印</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>历史时间线事件</t>
+          <t>喵史时间线事件</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2007-05-17</t>
+          <t/>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2007-06-11：WWDC Web 2.0应用</t>
+          <t>喵历 2007-06-11：万爪集会织网应用</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>历史时间线事件</t>
+          <t>喵史时间线事件</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2007-06-11</t>
+          <t/>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6121,22 +6121,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2007-06-18：玻璃与8小时通话</t>
+          <t>喵历 2007-06-18：玻璃爪面与八小时传声</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>历史时间线事件</t>
+          <t>喵史时间线事件</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2007-06-18</t>
+          <t/>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -6153,22 +6153,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2007-06-28：员工机与首发排队</t>
+          <t>喵历 2007-06-28：员工机与首发排队</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>历史时间线事件</t>
+          <t>喵史时间线事件</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>初代 iPhone</t>
+          <t>初代喵掌机</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2007-06-28</t>
+          <t/>
         </is>
       </c>
       <c r="F15" t="inlineStr">
